--- a/public/file/Employee Attendance Template.xlsx
+++ b/public/file/Employee Attendance Template.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\laragon\www\sonic\public\file\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{DBC626C5-EB53-43D0-A66B-80A66CA27991}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AAD1365D-F77A-4370-9C64-018A735EC349}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" xr2:uid="{0169F02F-17D1-4840-8497-1C895A5B1546}"/>
   </bookViews>
@@ -87,11 +87,15 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="49" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -410,22 +414,22 @@
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="13.6640625" customWidth="1"/>
-    <col min="2" max="2" width="30" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="41.109375" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="42.6640625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="30" style="3" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="41.109375" style="3" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="42.6640625" style="3" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:4" s="1" customFormat="1" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="B1" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="C1" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="D1" s="2" t="s">
         <v>2</v>
       </c>
     </row>

--- a/public/file/Employee Attendance Template.xlsx
+++ b/public/file/Employee Attendance Template.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="24701"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="24729"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\laragon\www\sonic\public\file\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AAD1365D-F77A-4370-9C64-018A735EC349}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C77FF87E-04A5-4B25-B33A-2D51D556C69E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" xr2:uid="{0169F02F-17D1-4840-8497-1C895A5B1546}"/>
   </bookViews>
@@ -34,23 +34,23 @@
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
 <sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4" uniqueCount="4">
   <si>
-    <t>Employee ID</t>
+    <t>User ID</t>
   </si>
   <si>
-    <t>Clock-in DateTime(yyyy-mm-dd hh:mm:ss)</t>
+    <t>Verify Mode</t>
   </si>
   <si>
-    <t>Clock-out DateTime(yyyy-mm-dd hh:mm:ss)</t>
+    <t>IO Mode</t>
   </si>
   <si>
-    <t>Attendance Date(yyyy-mm-dd)</t>
+    <t>IO Time</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2" x14ac:knownFonts="1">
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -65,6 +65,11 @@
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <name val="Calibri"/>
     </font>
   </fonts>
   <fills count="2">
@@ -92,10 +97,8 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="49" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -414,23 +417,23 @@
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="13.6640625" customWidth="1"/>
-    <col min="2" max="2" width="30" style="3" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="41.109375" style="3" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="42.6640625" style="3" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="30" style="2" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="41.109375" style="2" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="42.6640625" style="2" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:4" s="1" customFormat="1" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A1" s="1" t="s">
+      <c r="A1" s="3" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="C1" s="2" t="s">
+      <c r="B1" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="D1" s="2" t="s">
+      <c r="C1" s="3" t="s">
         <v>2</v>
+      </c>
+      <c r="D1" s="3" t="s">
+        <v>3</v>
       </c>
     </row>
   </sheetData>

--- a/public/file/Employee Attendance Template.xlsx
+++ b/public/file/Employee Attendance Template.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\laragon\www\sonic\public\file\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C77FF87E-04A5-4B25-B33A-2D51D556C69E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{989B4AC1-CD87-4300-B848-BBDD3CB58AE1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" xr2:uid="{0169F02F-17D1-4840-8497-1C895A5B1546}"/>
   </bookViews>
@@ -98,7 +98,7 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="49" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -416,7 +416,7 @@
   <dimension ref="A1:D1"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="13.6640625" customWidth="1"/>
+    <col min="1" max="1" width="13.6640625" style="2" customWidth="1"/>
     <col min="2" max="2" width="30" style="2" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="41.109375" style="2" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="42.6640625" style="2" bestFit="1" customWidth="1"/>
